--- a/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
+++ b/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6576818-D37B-4EEF-9FEB-43CC6DFF6411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F79A14-648F-4959-9CDA-632C549855E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitArms" sheetId="1" r:id="rId1"/>
@@ -847,7 +847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -856,8 +856,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -872,6 +879,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -905,17 +917,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -932,9 +947,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -972,9 +987,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1007,9 +1022,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1042,9 +1074,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1219,60 +1268,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1436,7 +1485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1647,7 @@
       </c>
       <c r="BB2" s="2"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
@@ -1761,7 +1810,7 @@
       </c>
       <c r="BB3" s="2"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>60</v>
       </c>
@@ -1924,7 +1973,7 @@
       </c>
       <c r="BB4" s="2"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2087,7 +2136,7 @@
       </c>
       <c r="BB5" s="2"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>63</v>
       </c>
@@ -2250,7 +2299,7 @@
       </c>
       <c r="BB6" s="2"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>65</v>
       </c>
@@ -2413,7 +2462,7 @@
       </c>
       <c r="BB7" s="2"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>66</v>
       </c>
@@ -2576,7 +2625,7 @@
       </c>
       <c r="BB8" s="2"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>67</v>
       </c>
@@ -2739,7 +2788,7 @@
       </c>
       <c r="BB9" s="2"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
@@ -2902,7 +2951,7 @@
       </c>
       <c r="BB10" s="2"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>69</v>
       </c>
@@ -3065,7 +3114,7 @@
       </c>
       <c r="BB11" s="2"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
@@ -3228,7 +3277,7 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>73</v>
       </c>
@@ -3391,7 +3440,7 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>74</v>
       </c>
@@ -3554,7 +3603,7 @@
       </c>
       <c r="BB14" s="2"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3637,8 @@
       <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="3">
-        <v>50</v>
+      <c r="L15" s="5">
+        <v>51</v>
       </c>
       <c r="M15" s="3">
         <v>-1</v>
@@ -3717,7 +3766,7 @@
       </c>
       <c r="BB15" s="2"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
@@ -3751,8 +3800,8 @@
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>50</v>
+      <c r="L16" s="5">
+        <v>51</v>
       </c>
       <c r="M16" s="3">
         <v>-1</v>
@@ -3880,7 +3929,7 @@
       </c>
       <c r="BB16" s="2"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>78</v>
       </c>
@@ -3914,8 +3963,8 @@
       <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
-        <v>50</v>
+      <c r="L17" s="5">
+        <v>51</v>
       </c>
       <c r="M17" s="3">
         <v>-1</v>
@@ -4043,7 +4092,7 @@
       </c>
       <c r="BB17" s="2"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>79</v>
       </c>
@@ -4206,7 +4255,7 @@
       </c>
       <c r="BB18" s="2"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>80</v>
       </c>
@@ -4369,7 +4418,7 @@
       </c>
       <c r="BB19" s="2"/>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>81</v>
       </c>
@@ -4532,7 +4581,7 @@
       </c>
       <c r="BB20" s="2"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -4695,7 +4744,7 @@
       </c>
       <c r="BB21" s="2"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>84</v>
       </c>
@@ -4858,7 +4907,7 @@
       </c>
       <c r="BB22" s="2"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
@@ -5021,7 +5070,7 @@
       </c>
       <c r="BB23" s="2"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>88</v>
       </c>
@@ -5184,7 +5233,7 @@
       </c>
       <c r="BB24" s="2"/>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>89</v>
       </c>
@@ -5347,7 +5396,7 @@
       </c>
       <c r="BB25" s="2"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>91</v>
       </c>
@@ -5510,7 +5559,7 @@
       </c>
       <c r="BB26" s="2"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>93</v>
       </c>
@@ -5673,7 +5722,7 @@
       </c>
       <c r="BB27" s="2"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>94</v>
       </c>
@@ -5836,7 +5885,7 @@
       </c>
       <c r="BB28" s="2"/>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>95</v>
       </c>
@@ -5999,7 +6048,7 @@
       </c>
       <c r="BB29" s="2"/>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>96</v>
       </c>
@@ -6162,7 +6211,7 @@
       </c>
       <c r="BB30" s="2"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
@@ -6325,7 +6374,7 @@
       </c>
       <c r="BB31" s="2"/>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>99</v>
       </c>
@@ -6488,7 +6537,7 @@
       </c>
       <c r="BB32" s="2"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
@@ -6651,7 +6700,7 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>102</v>
       </c>
@@ -6814,7 +6863,7 @@
       </c>
       <c r="BB34" s="2"/>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>103</v>
       </c>
@@ -6848,8 +6897,8 @@
       <c r="K35" s="2">
         <v>0</v>
       </c>
-      <c r="L35" s="3">
-        <v>50</v>
+      <c r="L35" s="5">
+        <v>51</v>
       </c>
       <c r="M35" s="3">
         <v>-1</v>
@@ -6977,7 +7026,7 @@
       </c>
       <c r="BB35" s="2"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>105</v>
       </c>
@@ -7011,8 +7060,8 @@
       <c r="K36" s="2">
         <v>0</v>
       </c>
-      <c r="L36" s="3">
-        <v>50</v>
+      <c r="L36" s="5">
+        <v>51</v>
       </c>
       <c r="M36" s="3">
         <v>-1</v>
@@ -7140,7 +7189,7 @@
       </c>
       <c r="BB36" s="2"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -7174,8 +7223,8 @@
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="3">
-        <v>50</v>
+      <c r="L37" s="5">
+        <v>51</v>
       </c>
       <c r="M37" s="3">
         <v>-1</v>
@@ -7303,7 +7352,7 @@
       </c>
       <c r="BB37" s="2"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>107</v>
       </c>
@@ -7466,7 +7515,7 @@
       </c>
       <c r="BB38" s="2"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>108</v>
       </c>
@@ -7629,7 +7678,7 @@
       </c>
       <c r="BB39" s="2"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>109</v>
       </c>
@@ -7792,7 +7841,7 @@
       </c>
       <c r="BB40" s="2"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>110</v>
       </c>
@@ -7955,7 +8004,7 @@
       </c>
       <c r="BB41" s="2"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>112</v>
       </c>
@@ -8118,7 +8167,7 @@
       </c>
       <c r="BB42" s="2"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>113</v>
       </c>
@@ -8281,7 +8330,7 @@
       </c>
       <c r="BB43" s="2"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>116</v>
       </c>
@@ -8444,7 +8493,7 @@
       </c>
       <c r="BB44" s="2"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>118</v>
       </c>
@@ -8607,7 +8656,7 @@
       </c>
       <c r="BB45" s="2"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>120</v>
       </c>
@@ -8770,7 +8819,7 @@
       </c>
       <c r="BB46" s="2"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>122</v>
       </c>
@@ -8933,7 +8982,7 @@
       </c>
       <c r="BB47" s="2"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>124</v>
       </c>
@@ -9096,7 +9145,7 @@
       </c>
       <c r="BB48" s="2"/>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>126</v>
       </c>
@@ -9259,7 +9308,7 @@
       </c>
       <c r="BB49" s="2"/>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>128</v>
       </c>
@@ -9422,7 +9471,7 @@
       </c>
       <c r="BB50" s="2"/>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -9585,7 +9634,7 @@
       </c>
       <c r="BB51" s="2"/>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>132</v>
       </c>
@@ -9748,7 +9797,7 @@
       </c>
       <c r="BB52" s="2"/>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>134</v>
       </c>
@@ -9911,7 +9960,7 @@
       </c>
       <c r="BB53" s="2"/>
     </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>136</v>
       </c>
@@ -10074,7 +10123,7 @@
       </c>
       <c r="BB54" s="2"/>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>138</v>
       </c>
@@ -10237,7 +10286,7 @@
       </c>
       <c r="BB55" s="2"/>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>140</v>
       </c>
@@ -10400,7 +10449,7 @@
       </c>
       <c r="BB56" s="2"/>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>142</v>
       </c>
@@ -10563,7 +10612,7 @@
       </c>
       <c r="BB57" s="2"/>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>144</v>
       </c>
@@ -10726,7 +10775,7 @@
       </c>
       <c r="BB58" s="2"/>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>146</v>
       </c>
@@ -10889,7 +10938,7 @@
       </c>
       <c r="BB59" s="2"/>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>148</v>
       </c>
@@ -11052,7 +11101,7 @@
       </c>
       <c r="BB60" s="2"/>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>150</v>
       </c>
@@ -11215,7 +11264,7 @@
       </c>
       <c r="BB61" s="2"/>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>152</v>
       </c>
@@ -11378,7 +11427,7 @@
       </c>
       <c r="BB62" s="2"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>154</v>
       </c>
@@ -11541,7 +11590,7 @@
       </c>
       <c r="BB63" s="2"/>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>157</v>
       </c>
@@ -11704,7 +11753,7 @@
       </c>
       <c r="BB64" s="2"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>159</v>
       </c>
@@ -11867,7 +11916,7 @@
       </c>
       <c r="BB65" s="2"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>161</v>
       </c>
@@ -12030,7 +12079,7 @@
       </c>
       <c r="BB66" s="2"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>163</v>
       </c>
@@ -12193,7 +12242,7 @@
       </c>
       <c r="BB67" s="2"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>165</v>
       </c>
@@ -12356,7 +12405,7 @@
       </c>
       <c r="BB68" s="2"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>167</v>
       </c>
@@ -12519,7 +12568,7 @@
       </c>
       <c r="BB69" s="2"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>169</v>
       </c>
@@ -12682,7 +12731,7 @@
       </c>
       <c r="BB70" s="2"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>171</v>
       </c>
@@ -12845,7 +12894,7 @@
       </c>
       <c r="BB71" s="2"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>173</v>
       </c>
@@ -13008,7 +13057,7 @@
       </c>
       <c r="BB72" s="2"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>175</v>
       </c>
@@ -13171,7 +13220,7 @@
       </c>
       <c r="BB73" s="2"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>177</v>
       </c>
@@ -13334,7 +13383,7 @@
       </c>
       <c r="BB74" s="2"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>179</v>
       </c>
@@ -13497,7 +13546,7 @@
       </c>
       <c r="BB75" s="2"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>181</v>
       </c>
@@ -13660,7 +13709,7 @@
       </c>
       <c r="BB76" s="2"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>183</v>
       </c>
@@ -13823,7 +13872,7 @@
       </c>
       <c r="BB77" s="2"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>185</v>
       </c>
@@ -13986,7 +14035,7 @@
       </c>
       <c r="BB78" s="2"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>187</v>
       </c>
@@ -14149,7 +14198,7 @@
       </c>
       <c r="BB79" s="2"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>189</v>
       </c>
@@ -14312,7 +14361,7 @@
       </c>
       <c r="BB80" s="2"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>191</v>
       </c>
@@ -14475,7 +14524,7 @@
       </c>
       <c r="BB81" s="2"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>193</v>
       </c>
@@ -14647,60 +14696,60 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BH82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="12" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>195</v>
       </c>
@@ -14882,7 +14931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>UnitArms!A2</f>
         <v>Code</v>
@@ -15094,7 +15143,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>UnitArms!A3</f>
         <v>unar001</v>
@@ -15306,7 +15355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>UnitArms!A4</f>
         <v>unar002</v>
@@ -15518,7 +15567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>UnitArms!A5</f>
         <v>unar003</v>
@@ -15730,7 +15779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>UnitArms!A6</f>
         <v>unar004</v>
@@ -15942,7 +15991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>UnitArms!A7</f>
         <v>unar005</v>
@@ -16154,7 +16203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>UnitArms!A8</f>
         <v>unar006</v>
@@ -16366,7 +16415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>UnitArms!A9</f>
         <v>unar007</v>
@@ -16578,7 +16627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>UnitArms!A10</f>
         <v>unar008</v>
@@ -16790,7 +16839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>UnitArms!A11</f>
         <v>unar009</v>
@@ -17002,7 +17051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>UnitArms!A12</f>
         <v>unar010</v>
@@ -17214,7 +17263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>UnitArms!A13</f>
         <v>unar011</v>
@@ -17426,7 +17475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>UnitArms!A14</f>
         <v>unar012</v>
@@ -17638,7 +17687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>UnitArms!A15</f>
         <v>unar013</v>
@@ -17778,7 +17827,7 @@
       </c>
       <c r="AO15">
         <f>UnitArms!L15</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP15">
         <f>UnitArms!N15</f>
@@ -17850,7 +17899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UnitArms!A16</f>
         <v>unar014</v>
@@ -17990,7 +18039,7 @@
       </c>
       <c r="AO16">
         <f>UnitArms!L16</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP16">
         <f>UnitArms!N16</f>
@@ -18062,7 +18111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UnitArms!A17</f>
         <v>unar015</v>
@@ -18202,7 +18251,7 @@
       </c>
       <c r="AO17">
         <f>UnitArms!L17</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP17">
         <f>UnitArms!N17</f>
@@ -18274,7 +18323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UnitArms!A18</f>
         <v>unar016</v>
@@ -18486,7 +18535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UnitArms!A19</f>
         <v>unar017</v>
@@ -18698,7 +18747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UnitArms!A20</f>
         <v>unar018</v>
@@ -18910,7 +18959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UnitArms!A21</f>
         <v>unar019</v>
@@ -19122,7 +19171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UnitArms!A22</f>
         <v>unar020</v>
@@ -19334,7 +19383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UnitArms!A23</f>
         <v>unar021</v>
@@ -19546,7 +19595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UnitArms!A24</f>
         <v>unar022</v>
@@ -19758,7 +19807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UnitArms!A25</f>
         <v>unar023</v>
@@ -19970,7 +20019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UnitArms!A26</f>
         <v>unar024</v>
@@ -20182,7 +20231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UnitArms!A27</f>
         <v>unar025</v>
@@ -20394,7 +20443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UnitArms!A28</f>
         <v>unar026</v>
@@ -20606,7 +20655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UnitArms!A29</f>
         <v>unar027</v>
@@ -20818,7 +20867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UnitArms!A30</f>
         <v>unar028</v>
@@ -21030,7 +21079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UnitArms!A31</f>
         <v>unar029</v>
@@ -21242,7 +21291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UnitArms!A32</f>
         <v>unar030</v>
@@ -21454,7 +21503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UnitArms!A33</f>
         <v>unar031</v>
@@ -21666,7 +21715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UnitArms!A34</f>
         <v>unar032</v>
@@ -21878,7 +21927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UnitArms!A35</f>
         <v>unar033</v>
@@ -22018,7 +22067,7 @@
       </c>
       <c r="AO35">
         <f>UnitArms!L35</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP35">
         <f>UnitArms!N35</f>
@@ -22090,7 +22139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UnitArms!A36</f>
         <v>unar034</v>
@@ -22230,7 +22279,7 @@
       </c>
       <c r="AO36">
         <f>UnitArms!L36</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP36">
         <f>UnitArms!N36</f>
@@ -22302,7 +22351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UnitArms!A37</f>
         <v>unar035</v>
@@ -22442,7 +22491,7 @@
       </c>
       <c r="AO37">
         <f>UnitArms!L37</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AP37">
         <f>UnitArms!N37</f>
@@ -22514,7 +22563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UnitArms!A38</f>
         <v>unar036</v>
@@ -22726,7 +22775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UnitArms!A39</f>
         <v>unar037</v>
@@ -22938,7 +22987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UnitArms!A40</f>
         <v>unar038</v>
@@ -23150,7 +23199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UnitArms!A41</f>
         <v>unar039</v>
@@ -23362,7 +23411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UnitArms!A42</f>
         <v>unar040</v>
@@ -23574,7 +23623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UnitArms!A43</f>
         <v>unar041</v>
@@ -23786,7 +23835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UnitArms!A44</f>
         <v>unar042</v>
@@ -23998,7 +24047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UnitArms!A45</f>
         <v>unar043</v>
@@ -24210,7 +24259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UnitArms!A46</f>
         <v>unar044</v>
@@ -24422,7 +24471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>UnitArms!A47</f>
         <v>unar045</v>
@@ -24634,7 +24683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>UnitArms!A48</f>
         <v>unar046</v>
@@ -24846,7 +24895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>UnitArms!A49</f>
         <v>unar047</v>
@@ -25058,7 +25107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>UnitArms!A50</f>
         <v>unar048</v>
@@ -25270,7 +25319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>UnitArms!A51</f>
         <v>unar049</v>
@@ -25482,7 +25531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>UnitArms!A52</f>
         <v>unar050</v>
@@ -25694,7 +25743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>UnitArms!A53</f>
         <v>unar051</v>
@@ -25906,7 +25955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>UnitArms!A54</f>
         <v>unar052</v>
@@ -26118,7 +26167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>UnitArms!A55</f>
         <v>unar053</v>
@@ -26330,7 +26379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>UnitArms!A56</f>
         <v>unar054</v>
@@ -26542,7 +26591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>UnitArms!A57</f>
         <v>unar055</v>
@@ -26754,7 +26803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>UnitArms!A58</f>
         <v>unar056</v>
@@ -26966,7 +27015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>UnitArms!A59</f>
         <v>unar057</v>
@@ -27178,7 +27227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>UnitArms!A60</f>
         <v>unar058</v>
@@ -27390,7 +27439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>UnitArms!A61</f>
         <v>unar059</v>
@@ -27602,7 +27651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>UnitArms!A62</f>
         <v>unar060</v>
@@ -27814,7 +27863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>UnitArms!A63</f>
         <v>unar061</v>
@@ -28026,7 +28075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>UnitArms!A64</f>
         <v>unar062</v>
@@ -28238,7 +28287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>UnitArms!A65</f>
         <v>unar063</v>
@@ -28450,7 +28499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>UnitArms!A66</f>
         <v>unar064</v>
@@ -28662,7 +28711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>UnitArms!A67</f>
         <v>unar065</v>
@@ -28874,7 +28923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>UnitArms!A68</f>
         <v>unar066</v>
@@ -29086,7 +29135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>UnitArms!A69</f>
         <v>unar067</v>
@@ -29298,7 +29347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>UnitArms!A70</f>
         <v>unar068</v>
@@ -29510,7 +29559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>UnitArms!A71</f>
         <v>unar069</v>
@@ -29722,7 +29771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>UnitArms!A72</f>
         <v>unar070</v>
@@ -29934,7 +29983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>UnitArms!A73</f>
         <v>unar071</v>
@@ -30146,7 +30195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>UnitArms!A74</f>
         <v>unar072</v>
@@ -30358,7 +30407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>UnitArms!A75</f>
         <v>unar073</v>
@@ -30570,7 +30619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>UnitArms!A76</f>
         <v>unar074</v>
@@ -30782,7 +30831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>UnitArms!A77</f>
         <v>unar075</v>
@@ -30994,7 +31043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>UnitArms!A78</f>
         <v>unar076</v>
@@ -31206,7 +31255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>UnitArms!A79</f>
         <v>unar077</v>
@@ -31418,7 +31467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>UnitArms!A80</f>
         <v>unar078</v>
@@ -31630,7 +31679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>UnitArms!A81</f>
         <v>unar079</v>
@@ -31842,7 +31891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>UnitArms!A82</f>
         <v>unar080</v>
@@ -32063,9 +32112,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C83"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -32076,7 +32125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>200</v>
       </c>
@@ -32085,7 +32134,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
@@ -32094,7 +32143,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -32103,7 +32152,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -32112,7 +32161,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -32121,7 +32170,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -32130,7 +32179,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -32139,7 +32188,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -32148,7 +32197,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -32157,7 +32206,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -32166,7 +32215,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -32175,7 +32224,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -32184,7 +32233,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -32193,7 +32242,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -32202,7 +32251,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -32211,7 +32260,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -32220,7 +32269,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -32229,7 +32278,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -32238,7 +32287,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -32247,7 +32296,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -32256,7 +32305,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -32265,7 +32314,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -32274,7 +32323,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -32283,7 +32332,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -32292,7 +32341,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -32301,7 +32350,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -32310,7 +32359,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -32319,7 +32368,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -32328,7 +32377,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -32337,7 +32386,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -32346,7 +32395,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -32355,7 +32404,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -32364,7 +32413,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -32373,7 +32422,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -32382,7 +32431,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -32391,7 +32440,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -32400,7 +32449,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -32409,7 +32458,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -32418,7 +32467,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -32427,7 +32476,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -32436,7 +32485,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -32445,7 +32494,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -32454,7 +32503,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -32463,7 +32512,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -32472,7 +32521,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -32481,7 +32530,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -32490,7 +32539,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -32499,7 +32548,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -32508,7 +32557,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -32517,7 +32566,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -32526,7 +32575,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -32535,7 +32584,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -32544,7 +32593,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -32553,7 +32602,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -32562,7 +32611,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -32571,7 +32620,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -32580,7 +32629,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -32589,7 +32638,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -32598,7 +32647,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -32607,7 +32656,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -32616,7 +32665,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -32625,7 +32674,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -32634,7 +32683,7 @@
       </c>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -32643,7 +32692,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -32652,7 +32701,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -32661,7 +32710,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -32670,7 +32719,7 @@
       </c>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>65</v>
       </c>
@@ -32679,7 +32728,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>66</v>
       </c>
@@ -32688,7 +32737,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>67</v>
       </c>
@@ -32697,7 +32746,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>68</v>
       </c>
@@ -32706,7 +32755,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>69</v>
       </c>
@@ -32715,7 +32764,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>70</v>
       </c>
@@ -32724,7 +32773,7 @@
       </c>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>71</v>
       </c>
@@ -32733,7 +32782,7 @@
       </c>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>72</v>
       </c>
@@ -32742,7 +32791,7 @@
       </c>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>73</v>
       </c>
@@ -32751,7 +32800,7 @@
       </c>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>74</v>
       </c>
@@ -32760,7 +32809,7 @@
       </c>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>75</v>
       </c>
@@ -32769,7 +32818,7 @@
       </c>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>76</v>
       </c>
@@ -32778,7 +32827,7 @@
       </c>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>77</v>
       </c>
@@ -32787,7 +32836,7 @@
       </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>78</v>
       </c>
@@ -32796,7 +32845,7 @@
       </c>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>79</v>
       </c>
@@ -32805,7 +32854,7 @@
       </c>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>80</v>
       </c>

--- a/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
+++ b/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F79A14-648F-4959-9CDA-632C549855E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA18EA5-8EB9-4459-8EC6-E0D32592D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -847,7 +847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,8 +863,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -884,6 +891,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -917,20 +929,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6700,168 +6717,168 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:54" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>8</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="6">
         <v>3</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="3">
-        <v>2</v>
-      </c>
-      <c r="H34" s="3">
+      <c r="G34" s="6">
+        <v>2</v>
+      </c>
+      <c r="H34" s="6">
         <v>5</v>
       </c>
-      <c r="I34" s="3">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="I34" s="6">
+        <v>1</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
         <v>48</v>
       </c>
-      <c r="M34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N34" s="3">
-        <v>2</v>
-      </c>
-      <c r="O34" s="3">
+      <c r="M34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="6">
+        <v>2</v>
+      </c>
+      <c r="O34" s="6">
         <v>93</v>
       </c>
-      <c r="P34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="2">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-      <c r="T34" s="3">
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="7">
+        <v>0</v>
+      </c>
+      <c r="S34" s="7">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6">
         <v>225</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="6">
         <v>1700</v>
       </c>
-      <c r="V34" s="2">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3">
+      <c r="V34" s="7">
+        <v>0</v>
+      </c>
+      <c r="W34" s="6">
         <v>16237</v>
       </c>
-      <c r="X34" s="3">
+      <c r="X34" s="6">
         <v>18040</v>
       </c>
-      <c r="Y34" s="3">
+      <c r="Y34" s="6">
         <v>50</v>
       </c>
-      <c r="Z34" s="2">
+      <c r="Z34" s="7">
         <v>50</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AA34" s="7">
         <v>50</v>
       </c>
-      <c r="AB34" s="3">
+      <c r="AB34" s="5">
         <v>459</v>
       </c>
-      <c r="AC34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
+      <c r="AC34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
         <v>1900000</v>
       </c>
-      <c r="AK34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="2">
+      <c r="AK34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="7">
         <v>38000</v>
       </c>
-      <c r="AN34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="2" t="str">
+      <c r="AN34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AQ34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>tunar032</v>
       </c>
-      <c r="AZ34" s="3">
+      <c r="AZ34" s="6">
         <v>9</v>
       </c>
-      <c r="BA34" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB34" s="2"/>
+      <c r="BA34" s="6">
+        <v>2</v>
+      </c>
+      <c r="BB34" s="7"/>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">

--- a/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
+++ b/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA18EA5-8EB9-4459-8EC6-E0D32592D3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9CA9AF-C309-4A1A-ABF8-599B9EB15E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6824,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>1900000</v>
+        <v>272727273</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="I34">
         <f>UnitArms!AJ34</f>
-        <v>1900000</v>
+        <v>272727273</v>
       </c>
       <c r="J34">
         <f>UnitArms!AK34</f>

--- a/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
+++ b/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9CA9AF-C309-4A1A-ABF8-599B9EB15E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271BF9BD-C5F4-41D1-9650-25CAEFEB2BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitArms" sheetId="1" r:id="rId1"/>
@@ -847,7 +847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -870,8 +870,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,6 +903,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -934,7 +953,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -944,6 +963,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -964,9 +990,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1004,9 +1030,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1039,26 +1065,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1091,26 +1100,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1293,7 +1285,7 @@
     <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
@@ -1360,7 +1352,7 @@
       <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -1524,7 +1516,7 @@
       <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="12" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -1686,7 +1678,7 @@
       <c r="G3" s="3">
         <v>1</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="13">
         <v>0</v>
       </c>
       <c r="I3" s="3">
@@ -1849,7 +1841,7 @@
       <c r="G4" s="3">
         <v>1</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="13">
         <v>0</v>
       </c>
       <c r="I4" s="3">
@@ -2012,7 +2004,7 @@
       <c r="G5" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="13">
         <v>0</v>
       </c>
       <c r="I5" s="3">
@@ -2175,7 +2167,7 @@
       <c r="G6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="13">
         <v>0</v>
       </c>
       <c r="I6" s="3">
@@ -2338,7 +2330,7 @@
       <c r="G7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="13">
         <v>0</v>
       </c>
       <c r="I7" s="3">
@@ -2501,7 +2493,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="13">
         <v>0</v>
       </c>
       <c r="I8" s="3">
@@ -2664,7 +2656,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="13">
         <v>0</v>
       </c>
       <c r="I9" s="3">
@@ -2827,7 +2819,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="13">
         <v>0</v>
       </c>
       <c r="I10" s="3">
@@ -2990,7 +2982,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="13">
         <v>0</v>
       </c>
       <c r="I11" s="3">
@@ -3153,7 +3145,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="13">
         <v>0</v>
       </c>
       <c r="I12" s="3">
@@ -3316,7 +3308,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="13">
         <v>0</v>
       </c>
       <c r="I13" s="3">
@@ -3457,168 +3449,168 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:54" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="9">
         <v>7</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="9">
         <v>3</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="G14" s="9">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
         <v>48</v>
       </c>
-      <c r="M14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="9">
+        <v>2</v>
+      </c>
+      <c r="O14" s="9">
         <v>93</v>
       </c>
-      <c r="P14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="P14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R14" s="10">
+        <v>0</v>
+      </c>
+      <c r="S14" s="10">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9">
         <v>40</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="9">
         <v>1700</v>
       </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="V14" s="10">
+        <v>0</v>
+      </c>
+      <c r="W14" s="9">
         <v>11241</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="9">
         <v>12489</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="9">
         <v>50</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z14" s="10">
         <v>30</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" s="10">
         <v>30</v>
       </c>
-      <c r="AB14" s="3">
-        <v>697</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>1900000</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="2">
-        <v>38000</v>
-      </c>
-      <c r="AN14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY14" s="2" t="str">
+      <c r="AB14" s="9">
+        <v>497</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="AE14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="6">
+        <v>4900000</v>
+      </c>
+      <c r="AK14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="6">
+        <v>490000</v>
+      </c>
+      <c r="AN14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tunar012</v>
       </c>
-      <c r="AZ14" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA14" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB14" s="2"/>
+      <c r="AZ14" s="9">
+        <v>1</v>
+      </c>
+      <c r="BA14" s="9">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="10"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -3642,7 +3634,7 @@
       <c r="G15" s="3">
         <v>1</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="13">
         <v>0</v>
       </c>
       <c r="I15" s="3">
@@ -3805,7 +3797,7 @@
       <c r="G16" s="3">
         <v>1</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="13">
         <v>0</v>
       </c>
       <c r="I16" s="3">
@@ -3968,7 +3960,7 @@
       <c r="G17" s="3">
         <v>1</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="13">
         <v>0</v>
       </c>
       <c r="I17" s="3">
@@ -4131,7 +4123,7 @@
       <c r="G18" s="3">
         <v>1</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="13">
         <v>0</v>
       </c>
       <c r="I18" s="3">
@@ -4294,7 +4286,7 @@
       <c r="G19" s="3">
         <v>1</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="13">
         <v>0</v>
       </c>
       <c r="I19" s="3">
@@ -4457,7 +4449,7 @@
       <c r="G20" s="3">
         <v>1</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="13">
         <v>0</v>
       </c>
       <c r="I20" s="3">
@@ -4620,7 +4612,7 @@
       <c r="G21" s="3">
         <v>1</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="13">
         <v>0</v>
       </c>
       <c r="I21" s="3">
@@ -4783,7 +4775,7 @@
       <c r="G22" s="3">
         <v>1</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="13">
         <v>0</v>
       </c>
       <c r="I22" s="3">
@@ -4946,8 +4938,8 @@
       <c r="G23" s="3">
         <v>2</v>
       </c>
-      <c r="H23" s="3">
-        <v>5</v>
+      <c r="H23" s="13">
+        <v>1</v>
       </c>
       <c r="I23" s="3">
         <v>1</v>
@@ -5109,8 +5101,8 @@
       <c r="G24" s="3">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>5</v>
+      <c r="H24" s="13">
+        <v>1</v>
       </c>
       <c r="I24" s="3">
         <v>1</v>
@@ -5272,8 +5264,8 @@
       <c r="G25" s="3">
         <v>4</v>
       </c>
-      <c r="H25" s="3">
-        <v>5</v>
+      <c r="H25" s="13">
+        <v>1</v>
       </c>
       <c r="I25" s="3">
         <v>1</v>
@@ -5435,8 +5427,8 @@
       <c r="G26" s="3">
         <v>2</v>
       </c>
-      <c r="H26" s="3">
-        <v>5</v>
+      <c r="H26" s="13">
+        <v>1</v>
       </c>
       <c r="I26" s="3">
         <v>1</v>
@@ -5598,8 +5590,8 @@
       <c r="G27" s="3">
         <v>4</v>
       </c>
-      <c r="H27" s="3">
-        <v>5</v>
+      <c r="H27" s="13">
+        <v>1</v>
       </c>
       <c r="I27" s="3">
         <v>1</v>
@@ -5761,8 +5753,8 @@
       <c r="G28" s="3">
         <v>4</v>
       </c>
-      <c r="H28" s="3">
-        <v>5</v>
+      <c r="H28" s="13">
+        <v>1</v>
       </c>
       <c r="I28" s="3">
         <v>1</v>
@@ -5924,8 +5916,8 @@
       <c r="G29" s="3">
         <v>4</v>
       </c>
-      <c r="H29" s="3">
-        <v>5</v>
+      <c r="H29" s="13">
+        <v>1</v>
       </c>
       <c r="I29" s="3">
         <v>1</v>
@@ -6087,8 +6079,8 @@
       <c r="G30" s="3">
         <v>2</v>
       </c>
-      <c r="H30" s="3">
-        <v>5</v>
+      <c r="H30" s="13">
+        <v>1</v>
       </c>
       <c r="I30" s="3">
         <v>1</v>
@@ -6250,8 +6242,8 @@
       <c r="G31" s="3">
         <v>4</v>
       </c>
-      <c r="H31" s="3">
-        <v>5</v>
+      <c r="H31" s="13">
+        <v>1</v>
       </c>
       <c r="I31" s="3">
         <v>1</v>
@@ -6413,8 +6405,8 @@
       <c r="G32" s="3">
         <v>2</v>
       </c>
-      <c r="H32" s="3">
-        <v>5</v>
+      <c r="H32" s="13">
+        <v>1</v>
       </c>
       <c r="I32" s="3">
         <v>1</v>
@@ -6576,8 +6568,8 @@
       <c r="G33" s="3">
         <v>2</v>
       </c>
-      <c r="H33" s="3">
-        <v>5</v>
+      <c r="H33" s="13">
+        <v>1</v>
       </c>
       <c r="I33" s="3">
         <v>1</v>
@@ -6739,8 +6731,8 @@
       <c r="G34" s="6">
         <v>2</v>
       </c>
-      <c r="H34" s="6">
-        <v>5</v>
+      <c r="H34" s="14">
+        <v>1</v>
       </c>
       <c r="I34" s="6">
         <v>1</v>
@@ -6824,7 +6816,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>272727273</v>
+        <v>4900000</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -6832,8 +6824,8 @@
       <c r="AL34" s="6">
         <v>1</v>
       </c>
-      <c r="AM34" s="7">
-        <v>38000</v>
+      <c r="AM34" s="6">
+        <v>490000</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -6902,8 +6894,8 @@
       <c r="G35" s="3">
         <v>2</v>
       </c>
-      <c r="H35" s="3">
-        <v>5</v>
+      <c r="H35" s="13">
+        <v>1</v>
       </c>
       <c r="I35" s="3">
         <v>1</v>
@@ -7065,8 +7057,8 @@
       <c r="G36" s="3">
         <v>2</v>
       </c>
-      <c r="H36" s="3">
-        <v>5</v>
+      <c r="H36" s="13">
+        <v>1</v>
       </c>
       <c r="I36" s="3">
         <v>1</v>
@@ -7228,8 +7220,8 @@
       <c r="G37" s="3">
         <v>2</v>
       </c>
-      <c r="H37" s="3">
-        <v>5</v>
+      <c r="H37" s="13">
+        <v>1</v>
       </c>
       <c r="I37" s="3">
         <v>1</v>
@@ -7391,8 +7383,8 @@
       <c r="G38" s="3">
         <v>2</v>
       </c>
-      <c r="H38" s="3">
-        <v>5</v>
+      <c r="H38" s="13">
+        <v>1</v>
       </c>
       <c r="I38" s="3">
         <v>1</v>
@@ -7554,8 +7546,8 @@
       <c r="G39" s="3">
         <v>2</v>
       </c>
-      <c r="H39" s="3">
-        <v>5</v>
+      <c r="H39" s="13">
+        <v>1</v>
       </c>
       <c r="I39" s="3">
         <v>1</v>
@@ -7717,8 +7709,8 @@
       <c r="G40" s="3">
         <v>2</v>
       </c>
-      <c r="H40" s="3">
-        <v>5</v>
+      <c r="H40" s="13">
+        <v>1</v>
       </c>
       <c r="I40" s="3">
         <v>1</v>
@@ -7880,8 +7872,8 @@
       <c r="G41" s="3">
         <v>2</v>
       </c>
-      <c r="H41" s="3">
-        <v>5</v>
+      <c r="H41" s="13">
+        <v>1</v>
       </c>
       <c r="I41" s="3">
         <v>1</v>
@@ -8043,8 +8035,8 @@
       <c r="G42" s="3">
         <v>2</v>
       </c>
-      <c r="H42" s="3">
-        <v>5</v>
+      <c r="H42" s="13">
+        <v>1</v>
       </c>
       <c r="I42" s="3">
         <v>1</v>
@@ -8206,7 +8198,7 @@
       <c r="G43" s="3">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="13">
         <v>1</v>
       </c>
       <c r="I43" s="3">
@@ -8369,7 +8361,7 @@
       <c r="G44" s="3">
         <v>3</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="13">
         <v>1</v>
       </c>
       <c r="I44" s="3">
@@ -8532,7 +8524,7 @@
       <c r="G45" s="3">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="13">
         <v>1</v>
       </c>
       <c r="I45" s="3">
@@ -8695,7 +8687,7 @@
       <c r="G46" s="3">
         <v>3</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="13">
         <v>1</v>
       </c>
       <c r="I46" s="3">
@@ -8858,7 +8850,7 @@
       <c r="G47" s="3">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="13">
         <v>1</v>
       </c>
       <c r="I47" s="3">
@@ -9021,7 +9013,7 @@
       <c r="G48" s="3">
         <v>3</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="13">
         <v>1</v>
       </c>
       <c r="I48" s="3">
@@ -9184,7 +9176,7 @@
       <c r="G49" s="3">
         <v>3</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="13">
         <v>1</v>
       </c>
       <c r="I49" s="3">
@@ -9347,7 +9339,7 @@
       <c r="G50" s="3">
         <v>3</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="13">
         <v>1</v>
       </c>
       <c r="I50" s="3">
@@ -9510,7 +9502,7 @@
       <c r="G51" s="3">
         <v>3</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="13">
         <v>1</v>
       </c>
       <c r="I51" s="3">
@@ -9673,7 +9665,7 @@
       <c r="G52" s="3">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="13">
         <v>1</v>
       </c>
       <c r="I52" s="3">
@@ -9836,7 +9828,7 @@
       <c r="G53" s="3">
         <v>3</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="13">
         <v>1</v>
       </c>
       <c r="I53" s="3">
@@ -9999,7 +9991,7 @@
       <c r="G54" s="3">
         <v>3</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="13">
         <v>1</v>
       </c>
       <c r="I54" s="3">
@@ -10162,7 +10154,7 @@
       <c r="G55" s="3">
         <v>3</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="13">
         <v>1</v>
       </c>
       <c r="I55" s="3">
@@ -10325,7 +10317,7 @@
       <c r="G56" s="3">
         <v>3</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="13">
         <v>1</v>
       </c>
       <c r="I56" s="3">
@@ -10488,7 +10480,7 @@
       <c r="G57" s="3">
         <v>3</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="13">
         <v>1</v>
       </c>
       <c r="I57" s="3">
@@ -10651,7 +10643,7 @@
       <c r="G58" s="3">
         <v>3</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="13">
         <v>1</v>
       </c>
       <c r="I58" s="3">
@@ -10814,7 +10806,7 @@
       <c r="G59" s="3">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="13">
         <v>1</v>
       </c>
       <c r="I59" s="3">
@@ -10977,7 +10969,7 @@
       <c r="G60" s="3">
         <v>3</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="13">
         <v>1</v>
       </c>
       <c r="I60" s="3">
@@ -11140,7 +11132,7 @@
       <c r="G61" s="3">
         <v>3</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61" s="13">
         <v>1</v>
       </c>
       <c r="I61" s="3">
@@ -11303,7 +11295,7 @@
       <c r="G62" s="3">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="13">
         <v>1</v>
       </c>
       <c r="I62" s="3">
@@ -11466,7 +11458,7 @@
       <c r="G63" s="3">
         <v>4</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63" s="13">
         <v>1</v>
       </c>
       <c r="I63" s="3">
@@ -11629,7 +11621,7 @@
       <c r="G64" s="3">
         <v>4</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64" s="13">
         <v>1</v>
       </c>
       <c r="I64" s="3">
@@ -11792,7 +11784,7 @@
       <c r="G65" s="3">
         <v>4</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65" s="13">
         <v>1</v>
       </c>
       <c r="I65" s="3">
@@ -11955,7 +11947,7 @@
       <c r="G66" s="3">
         <v>4</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66" s="13">
         <v>1</v>
       </c>
       <c r="I66" s="3">
@@ -12118,7 +12110,7 @@
       <c r="G67" s="3">
         <v>4</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67" s="13">
         <v>1</v>
       </c>
       <c r="I67" s="3">
@@ -12281,7 +12273,7 @@
       <c r="G68" s="3">
         <v>4</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68" s="13">
         <v>1</v>
       </c>
       <c r="I68" s="3">
@@ -12444,7 +12436,7 @@
       <c r="G69" s="3">
         <v>4</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69" s="13">
         <v>1</v>
       </c>
       <c r="I69" s="3">
@@ -12607,7 +12599,7 @@
       <c r="G70" s="3">
         <v>4</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H70" s="13">
         <v>1</v>
       </c>
       <c r="I70" s="3">
@@ -12770,7 +12762,7 @@
       <c r="G71" s="3">
         <v>4</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71" s="13">
         <v>1</v>
       </c>
       <c r="I71" s="3">
@@ -12933,7 +12925,7 @@
       <c r="G72" s="3">
         <v>4</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="13">
         <v>1</v>
       </c>
       <c r="I72" s="3">
@@ -13096,7 +13088,7 @@
       <c r="G73" s="3">
         <v>4</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73" s="13">
         <v>1</v>
       </c>
       <c r="I73" s="3">
@@ -13259,7 +13251,7 @@
       <c r="G74" s="3">
         <v>4</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74" s="13">
         <v>1</v>
       </c>
       <c r="I74" s="3">
@@ -13422,7 +13414,7 @@
       <c r="G75" s="3">
         <v>4</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75" s="13">
         <v>1</v>
       </c>
       <c r="I75" s="3">
@@ -13585,7 +13577,7 @@
       <c r="G76" s="3">
         <v>4</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H76" s="13">
         <v>1</v>
       </c>
       <c r="I76" s="3">
@@ -13748,7 +13740,7 @@
       <c r="G77" s="3">
         <v>4</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77" s="13">
         <v>1</v>
       </c>
       <c r="I77" s="3">
@@ -13911,7 +13903,7 @@
       <c r="G78" s="3">
         <v>4</v>
       </c>
-      <c r="H78" s="3">
+      <c r="H78" s="13">
         <v>1</v>
       </c>
       <c r="I78" s="3">
@@ -14074,7 +14066,7 @@
       <c r="G79" s="3">
         <v>4</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79" s="13">
         <v>1</v>
       </c>
       <c r="I79" s="3">
@@ -14237,7 +14229,7 @@
       <c r="G80" s="3">
         <v>4</v>
       </c>
-      <c r="H80" s="3">
+      <c r="H80" s="13">
         <v>1</v>
       </c>
       <c r="I80" s="3">
@@ -14400,7 +14392,7 @@
       <c r="G81" s="3">
         <v>4</v>
       </c>
-      <c r="H81" s="3">
+      <c r="H81" s="13">
         <v>1</v>
       </c>
       <c r="I81" s="3">
@@ -14563,7 +14555,7 @@
       <c r="G82" s="3">
         <v>4</v>
       </c>
-      <c r="H82" s="3">
+      <c r="H82" s="13">
         <v>1</v>
       </c>
       <c r="I82" s="3">
@@ -17524,7 +17516,7 @@
       </c>
       <c r="I14">
         <f>UnitArms!AJ14</f>
-        <v>1900000</v>
+        <v>4900000</v>
       </c>
       <c r="J14">
         <f>UnitArms!AK14</f>
@@ -17586,7 +17578,7 @@
       </c>
       <c r="AB14">
         <f>UnitArms!AB14</f>
-        <v>697</v>
+        <v>497</v>
       </c>
       <c r="AC14">
         <f>UnitArms!AE14</f>
@@ -19586,7 +19578,7 @@
       </c>
       <c r="BA23">
         <f>UnitArms!H23</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB23">
         <f>UnitArms!W23</f>
@@ -19798,7 +19790,7 @@
       </c>
       <c r="BA24">
         <f>UnitArms!H24</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB24">
         <f>UnitArms!W24</f>
@@ -20010,7 +20002,7 @@
       </c>
       <c r="BA25">
         <f>UnitArms!H25</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB25">
         <f>UnitArms!W25</f>
@@ -20222,7 +20214,7 @@
       </c>
       <c r="BA26">
         <f>UnitArms!H26</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB26">
         <f>UnitArms!W26</f>
@@ -20434,7 +20426,7 @@
       </c>
       <c r="BA27">
         <f>UnitArms!H27</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB27">
         <f>UnitArms!W27</f>
@@ -20646,7 +20638,7 @@
       </c>
       <c r="BA28">
         <f>UnitArms!H28</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB28">
         <f>UnitArms!W28</f>
@@ -20858,7 +20850,7 @@
       </c>
       <c r="BA29">
         <f>UnitArms!H29</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB29">
         <f>UnitArms!W29</f>
@@ -21070,7 +21062,7 @@
       </c>
       <c r="BA30">
         <f>UnitArms!H30</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB30">
         <f>UnitArms!W30</f>
@@ -21282,7 +21274,7 @@
       </c>
       <c r="BA31">
         <f>UnitArms!H31</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB31">
         <f>UnitArms!W31</f>
@@ -21494,7 +21486,7 @@
       </c>
       <c r="BA32">
         <f>UnitArms!H32</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB32">
         <f>UnitArms!W32</f>
@@ -21706,7 +21698,7 @@
       </c>
       <c r="BA33">
         <f>UnitArms!H33</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB33">
         <f>UnitArms!W33</f>
@@ -21764,7 +21756,7 @@
       </c>
       <c r="I34">
         <f>UnitArms!AJ34</f>
-        <v>272727273</v>
+        <v>4900000</v>
       </c>
       <c r="J34">
         <f>UnitArms!AK34</f>
@@ -21918,7 +21910,7 @@
       </c>
       <c r="BA34">
         <f>UnitArms!H34</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB34">
         <f>UnitArms!W34</f>
@@ -22130,7 +22122,7 @@
       </c>
       <c r="BA35">
         <f>UnitArms!H35</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB35">
         <f>UnitArms!W35</f>
@@ -22342,7 +22334,7 @@
       </c>
       <c r="BA36">
         <f>UnitArms!H36</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB36">
         <f>UnitArms!W36</f>
@@ -22554,7 +22546,7 @@
       </c>
       <c r="BA37">
         <f>UnitArms!H37</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB37">
         <f>UnitArms!W37</f>
@@ -22766,7 +22758,7 @@
       </c>
       <c r="BA38">
         <f>UnitArms!H38</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB38">
         <f>UnitArms!W38</f>
@@ -22978,7 +22970,7 @@
       </c>
       <c r="BA39">
         <f>UnitArms!H39</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB39">
         <f>UnitArms!W39</f>
@@ -23190,7 +23182,7 @@
       </c>
       <c r="BA40">
         <f>UnitArms!H40</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB40">
         <f>UnitArms!W40</f>
@@ -23402,7 +23394,7 @@
       </c>
       <c r="BA41">
         <f>UnitArms!H41</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB41">
         <f>UnitArms!W41</f>
@@ -23614,7 +23606,7 @@
       </c>
       <c r="BA42">
         <f>UnitArms!H42</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB42">
         <f>UnitArms!W42</f>

--- a/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
+++ b/gu_in/Item.edf/40_UnitArms/UnitArms.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271BF9BD-C5F4-41D1-9650-25CAEFEB2BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1FF2A3-C7D2-4957-ABA4-B4EE9A3DD915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitArms" sheetId="1" r:id="rId1"/>
@@ -990,9 +990,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1030,9 +1030,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1065,9 +1065,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1100,9 +1117,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6816,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>4900000</v>
+        <v>36363637</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -6825,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="6">
-        <v>490000</v>
+        <v>4545455</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -21756,7 +21790,7 @@
       </c>
       <c r="I34">
         <f>UnitArms!AJ34</f>
-        <v>4900000</v>
+        <v>36363637</v>
       </c>
       <c r="J34">
         <f>UnitArms!AK34</f>
